--- a/output/pdf_financials_xlsx/DMX.xlsx
+++ b/output/pdf_financials_xlsx/DMX.xlsx
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>7.693858</v>
+        <v>-7.693858</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.12349</v>
+        <v>-0.12349</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.14133</v>
+        <v>-0.14133</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.967668</v>
+        <v>-0.967668</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.09056</v>
+        <v>-1.09056</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.72988</v>
+        <v>-2.72988</v>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
@@ -1839,13 +1839,13 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>7.693858</v>
+        <v>-7.693858</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.12349</v>
+        <v>-0.12349</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.14133</v>
+        <v>-0.14133</v>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.967668</v>
+        <v>-0.967668</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.09056</v>
+        <v>-1.09056</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.72988</v>
+        <v>-2.72988</v>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>7.693858</v>
+        <v>-7.693858</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.12349</v>
+        <v>-0.12349</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.14133</v>
+        <v>-0.14133</v>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.967668</v>
+        <v>-0.967668</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.09056</v>
+        <v>-1.09056</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.72988</v>
+        <v>-2.72988</v>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
@@ -2329,13 +2329,13 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>32.2556</v>
+        <v>-32.2556</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>36.352</v>
+        <v>-36.352</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>68.247</v>
+        <v>-68.247</v>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.700335</v>
+        <v>-7.687381</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.12349</v>
+        <v>-0.12349</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.14133</v>
+        <v>-0.14133</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.967668</v>
+        <v>-0.967668</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.09056</v>
+        <v>-1.09056</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.72988</v>
+        <v>-2.72988</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -2543,13 +2543,13 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>7.700335</v>
+        <v>-7.687381</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.12349</v>
+        <v>-0.12349</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.14133</v>
+        <v>-0.14133</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.967668</v>
+        <v>-0.967668</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.09056</v>
+        <v>-1.09056</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.72988</v>
+        <v>-2.72988</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
@@ -2721,13 +2721,13 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         <v>0.42069</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.891254</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.1074</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
@@ -6425,22 +6425,22 @@
         <v>0</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.100559</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.953659</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.307702</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.47406</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.086801</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.104799</v>
       </c>
     </row>
     <row r="93">
@@ -10934,7 +10934,11 @@
           <t>Reserves (Notes 11 and 12)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11498,7 +11502,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11997,7 +12005,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -12500,7 +12512,11 @@
           <t>Reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -13534,7 +13550,11 @@
           <t>Reserve (Note 9) 585,900</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -15061,7 +15081,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -15877,7 +15901,11 @@
           <t>Reserves (note 12)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -43113,13 +43141,13 @@
         </is>
       </c>
       <c r="O334" s="5" t="n">
-        <v>0.967668</v>
+        <v>-0.967668</v>
       </c>
       <c r="P334" s="5" t="n">
-        <v>1.09056</v>
+        <v>-1.09056</v>
       </c>
       <c r="Q334" s="5" t="n">
-        <v>2.72988</v>
+        <v>-2.72988</v>
       </c>
       <c r="R334" t="inlineStr">
         <is>
@@ -44323,7 +44351,7 @@
         </is>
       </c>
       <c r="M346" s="5" t="n">
-        <v>0.14133</v>
+        <v>-0.14133</v>
       </c>
       <c r="N346" t="inlineStr">
         <is>
@@ -45233,10 +45261,10 @@
         </is>
       </c>
       <c r="L355" s="5" t="n">
-        <v>0.12349</v>
+        <v>-0.12349</v>
       </c>
       <c r="M355" s="5" t="n">
-        <v>0.14133</v>
+        <v>-0.14133</v>
       </c>
       <c r="N355" t="inlineStr">
         <is>
@@ -46852,10 +46880,10 @@
         </is>
       </c>
       <c r="K371" s="5" t="n">
-        <v>7.693858</v>
+        <v>-7.693858</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>0.12349</v>
+        <v>-0.12349</v>
       </c>
       <c r="M371" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DMX.xlsx
+++ b/output/pdf_financials_xlsx/DMX.xlsx
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001538</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002249</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.318785</v>
+        <v>-0.320323</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.07449600000000001</v>
+        <v>-0.07674499999999999</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.301147</v>
+        <v>-0.302685</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.061937</v>
+        <v>-0.06418600000000001</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-512.4772390790123</v>
+        <v>-515.0945322737097</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-72.64825936004505</v>
+        <v>-75.28619686590973</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -2870,19 +2870,19 @@
         <v>0.026141</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002069</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.004296</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.007154</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.427306</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.427306</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>2.512091</v>
@@ -2986,19 +2986,19 @@
         <v>0.026141</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.002069</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.004296</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.007154</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.427306</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.427306</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>2.512091</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.433514</v>
+        <v>0.006208</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.012733</v>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -47753,7 +47753,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
